--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150727</v>
+        <v>121150729</v>
       </c>
       <c r="B4" t="n">
-        <v>57192</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,21 +964,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100096</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515191</v>
+        <v>514740</v>
       </c>
       <c r="R4" t="n">
-        <v>6637012</v>
+        <v>6636586</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150726</v>
+        <v>121150728</v>
       </c>
       <c r="B5" t="n">
-        <v>57317</v>
+        <v>57720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100136</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514859</v>
+        <v>514848</v>
       </c>
       <c r="R5" t="n">
-        <v>6636665</v>
+        <v>6636612</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150729</v>
+        <v>121150727</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>57195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514740</v>
+        <v>515191</v>
       </c>
       <c r="R6" t="n">
-        <v>6636586</v>
+        <v>6637012</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150728</v>
+        <v>121150726</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,25 +1293,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100136</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514848</v>
+        <v>514859</v>
       </c>
       <c r="R7" t="n">
-        <v>6636612</v>
+        <v>6636665</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150728</v>
+        <v>121150726</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514848</v>
+        <v>514859</v>
       </c>
       <c r="R5" t="n">
-        <v>6636612</v>
+        <v>6636665</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150727</v>
+        <v>121150728</v>
       </c>
       <c r="B6" t="n">
-        <v>57195</v>
+        <v>57720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515191</v>
+        <v>514848</v>
       </c>
       <c r="R6" t="n">
-        <v>6637012</v>
+        <v>6636612</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150726</v>
+        <v>121150727</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>57195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,25 +1293,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100136</v>
+        <v>100096</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514859</v>
+        <v>515191</v>
       </c>
       <c r="R7" t="n">
-        <v>6636665</v>
+        <v>6637012</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150729</v>
+        <v>121150726</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,25 +960,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100136</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514740</v>
+        <v>514859</v>
       </c>
       <c r="R4" t="n">
-        <v>6636586</v>
+        <v>6636665</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150726</v>
+        <v>121150729</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100136</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514859</v>
+        <v>514740</v>
       </c>
       <c r="R5" t="n">
-        <v>6636665</v>
+        <v>6636586</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150726</v>
+        <v>121150727</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,25 +960,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100136</v>
+        <v>100096</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514859</v>
+        <v>515191</v>
       </c>
       <c r="R4" t="n">
-        <v>6636665</v>
+        <v>6637012</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150729</v>
+        <v>121150726</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514740</v>
+        <v>514859</v>
       </c>
       <c r="R5" t="n">
-        <v>6636586</v>
+        <v>6636665</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150728</v>
+        <v>121150729</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514848</v>
+        <v>514740</v>
       </c>
       <c r="R6" t="n">
-        <v>6636612</v>
+        <v>6636586</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150727</v>
+        <v>121150728</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,16 +1297,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100096</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515191</v>
+        <v>514848</v>
       </c>
       <c r="R7" t="n">
-        <v>6637012</v>
+        <v>6636612</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150726</v>
+        <v>121150728</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>57720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100136</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514859</v>
+        <v>514848</v>
       </c>
       <c r="R5" t="n">
-        <v>6636665</v>
+        <v>6636612</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150729</v>
+        <v>121150726</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,25 +1182,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100136</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514740</v>
+        <v>514859</v>
       </c>
       <c r="R6" t="n">
-        <v>6636586</v>
+        <v>6636665</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150728</v>
+        <v>121150729</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>91986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,21 +1297,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514848</v>
+        <v>514740</v>
       </c>
       <c r="R7" t="n">
-        <v>6636612</v>
+        <v>6636586</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150727</v>
+        <v>121150729</v>
       </c>
       <c r="B4" t="n">
-        <v>57195</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,21 +964,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100096</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515191</v>
+        <v>514740</v>
       </c>
       <c r="R4" t="n">
-        <v>6637012</v>
+        <v>6636586</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1062,7 +1062,7 @@
         <v>121150728</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150726</v>
+        <v>121150727</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,25 +1182,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100136</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514859</v>
+        <v>515191</v>
       </c>
       <c r="R6" t="n">
-        <v>6636665</v>
+        <v>6637012</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150729</v>
+        <v>121150726</v>
       </c>
       <c r="B7" t="n">
-        <v>91986</v>
+        <v>57323</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,25 +1293,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100136</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514740</v>
+        <v>514859</v>
       </c>
       <c r="R7" t="n">
-        <v>6636586</v>
+        <v>6636665</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150728</v>
+        <v>121150726</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514848</v>
+        <v>514859</v>
       </c>
       <c r="R5" t="n">
-        <v>6636612</v>
+        <v>6636665</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150727</v>
+        <v>121150728</v>
       </c>
       <c r="B6" t="n">
-        <v>57198</v>
+        <v>57723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515191</v>
+        <v>514848</v>
       </c>
       <c r="R6" t="n">
-        <v>6637012</v>
+        <v>6636612</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150726</v>
+        <v>121150727</v>
       </c>
       <c r="B7" t="n">
-        <v>57323</v>
+        <v>57198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,25 +1293,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100136</v>
+        <v>100096</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514859</v>
+        <v>515191</v>
       </c>
       <c r="R7" t="n">
-        <v>6636665</v>
+        <v>6637012</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -1284,11 +1284,11 @@
         <v>121150727</v>
       </c>
       <c r="B7" t="n">
-        <v>57198</v>
+        <v>57201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -1173,11 +1173,11 @@
         <v>121150728</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80144657</v>
+        <v>80156148</v>
       </c>
       <c r="B2" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515207.9466066007</v>
+        <v>515020</v>
       </c>
       <c r="R2" t="n">
-        <v>6637030.230179185</v>
+        <v>6636913</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,24 +754,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>under två gamla tallar vid stranden</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +771,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrskog med renlavar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,64 +794,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80139675</v>
+        <v>121150729</v>
       </c>
       <c r="B3" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vikmossen Ö om, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514736.7527611047</v>
+        <v>514740</v>
       </c>
       <c r="R3" t="n">
-        <v>6636616.025844406</v>
+        <v>6636586</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,95 +863,69 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rent gula frk som blir beige-bruna med åldern. Foten smal. Frk fast och grenar ut från den smala vita basen till en brett tuvad och fast frk. Doftar jord. Skador av tryck/skrap är vinrödbruna. Under tall bland grå renlav. I gallrat 78-årigt tallbestånd på moränmark. Osäker artbestämning eftersom jag ej sett den tidigare, ej mikroskoperat den och ej fått den bekräftad av någon med erfarenhet av den.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lingontallskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gallrad 78-årig tallskog på morän, med husmossa, väggmossa och grå renlav i bottenskiktet och mest lingon i fältskiktet.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Andersson, Emil Pagstedt Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150729</v>
+        <v>80144657</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -986,19 +933,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kloten, Vstm</t>
+          <t>Hälludden, Stora Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514740</v>
+        <v>515208</v>
       </c>
       <c r="R4" t="n">
-        <v>6636586</v>
+        <v>6637030</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,17 +976,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>under två gamla tallar vid stranden</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,55 +995,56 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150726</v>
+        <v>121150727</v>
       </c>
       <c r="B5" t="n">
-        <v>57343</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100136</v>
+        <v>100096</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514859</v>
+        <v>515191</v>
       </c>
       <c r="R5" t="n">
-        <v>6636665</v>
+        <v>6637012</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,37 +1125,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150728</v>
+        <v>121150726</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100136</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514848</v>
+        <v>514859</v>
       </c>
       <c r="R6" t="n">
-        <v>6636612</v>
+        <v>6636665</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,12 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1281,15 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150727</v>
+        <v>121150728</v>
       </c>
       <c r="B7" t="n">
-        <v>57213</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,16 +1242,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100096</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515191</v>
+        <v>514848</v>
       </c>
       <c r="R7" t="n">
-        <v>6637012</v>
+        <v>6636612</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1389,6 +1334,130 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80139675</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vikmossen Ö om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514737</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6636616</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rent gula frk som blir beige-bruna med åldern. Foten smal. Frk fast och grenar ut från den smala vita basen till en brett tuvad och fast frk. Doftar jord. Skador av tryck/skrap är vinrödbruna. Under tall bland grå renlav. I gallrat 78-årigt tallbestånd på moränmark. Osäker artbestämning eftersom jag ej sett den tidigare, ej mikroskoperat den och ej fått den bekräftad av någon med erfarenhet av den.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lingontallskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gallrad 78-årig tallskog på morän, med husmossa, väggmossa och grå renlav i bottenskiktet och mest lingon i fältskiktet.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43429-2024 artfynd.xlsx
+++ b/artfynd/A 43429-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80156148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150729</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80144657</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150727</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150726</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150728</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,8 +1493,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80139675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>